--- a/app/src/main/java/com/example/methodmesh/core/scheduling/docs/example_odk_scheduler.xlsx
+++ b/app/src/main/java/com/example/methodmesh/core/scheduling/docs/example_odk_scheduler.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ree0e60d807ce4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4d0718fd5b9349f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rbffcb39342d4401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R3acabc9681934dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R98c4174a97654ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R6bbddfa9b06b4f13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -643,8 +643,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -652,35 +654,37 @@
         <x:v>form_title</x:v>
       </x:c>
       <x:c r="B1" s="17" t="str">
-        <x:v>scheduler</x:v>
-      </x:c>
-      <x:c r="C1" s="25"/>
-      <x:c r="D1" s="25"/>
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" s="25" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="D1" s="25" t="str">
+        <x:v>default_language</x:v>
+      </x:c>
       <x:c r="E1" s="25"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="6" t="str">
-        <x:v>form_id</x:v>
+        <x:v>MethodMesh Scheduler</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
         <x:v>methodmesh_scheduler</x:v>
       </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2026092201</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>English</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="6" t="str">
-        <x:v>version</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>2026072701</x:v>
-      </x:c>
+      <x:c r="A3" s="6"/>
+      <x:c r="B3" s="8"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>default_language</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>English</x:v>
-      </x:c>
+      <x:c r="A4" s="9"/>
+      <x:c r="B4" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
